--- a/research/traditional_assets/database/data/mexico/mexico_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0579</v>
+        <v>0.0518</v>
       </c>
       <c r="E2">
-        <v>0.009849999999999999</v>
+        <v>0.101</v>
       </c>
       <c r="F2">
-        <v>0.157</v>
+        <v>0.20725</v>
       </c>
       <c r="G2">
-        <v>0.2137045668261172</v>
+        <v>0.0756336328282151</v>
       </c>
       <c r="H2">
-        <v>0.2076536244327241</v>
+        <v>0.06591122435295695</v>
       </c>
       <c r="I2">
-        <v>0.2012347193262194</v>
+        <v>0.07368915113316347</v>
       </c>
       <c r="J2">
-        <v>0.1512549106904366</v>
+        <v>0.05469819686103484</v>
       </c>
       <c r="K2">
-        <v>342.8</v>
+        <v>380.1</v>
       </c>
       <c r="L2">
-        <v>0.1401529089496709</v>
+        <v>0.2548612042376291</v>
       </c>
       <c r="M2">
-        <v>160</v>
+        <v>108.86</v>
       </c>
       <c r="N2">
-        <v>0.039907215723443</v>
+        <v>0.03091647496520974</v>
       </c>
       <c r="O2">
-        <v>0.4667444574095683</v>
+        <v>0.2863983162325703</v>
       </c>
       <c r="P2">
-        <v>98.25</v>
+        <v>90.19</v>
       </c>
       <c r="Q2">
-        <v>0.02450552465517671</v>
+        <v>0.02561415466757547</v>
       </c>
       <c r="R2">
-        <v>0.286610268378063</v>
+        <v>0.2372796632465141</v>
       </c>
       <c r="S2">
-        <v>61.74999999999999</v>
+        <v>18.67</v>
       </c>
       <c r="T2">
-        <v>0.3859374999999999</v>
+        <v>0.1715046849164064</v>
       </c>
       <c r="U2">
-        <v>2248.7</v>
+        <v>983</v>
       </c>
       <c r="V2">
-        <v>0.5608709749831642</v>
+        <v>0.2791741217233251</v>
       </c>
       <c r="W2">
-        <v>0.1068247179003786</v>
+        <v>0.2291771832407875</v>
       </c>
       <c r="X2">
-        <v>0.0433816898429266</v>
+        <v>0.06094725237638184</v>
       </c>
       <c r="Y2">
-        <v>0.06344302805745203</v>
+        <v>0.1682299308644056</v>
       </c>
       <c r="Z2">
-        <v>0.2662233058319002</v>
+        <v>0.3888816458501735</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03387738421221383</v>
+        <v>0.05945587851241461</v>
       </c>
       <c r="AC2">
-        <v>-0.03127172655233125</v>
+        <v>-0.05945587851241461</v>
       </c>
       <c r="AD2">
-        <v>9613.299999999999</v>
+        <v>3734.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>9613.299999999999</v>
+        <v>3734.8</v>
       </c>
       <c r="AG2">
-        <v>7364.599999999999</v>
+        <v>2751.8</v>
       </c>
       <c r="AH2">
-        <v>0.7056876073583604</v>
+        <v>0.5147259471602421</v>
       </c>
       <c r="AI2">
-        <v>0.6977485193357333</v>
+        <v>0.6262870174732535</v>
       </c>
       <c r="AJ2">
-        <v>0.6474999780198525</v>
+        <v>0.4386806740104259</v>
       </c>
       <c r="AK2">
-        <v>0.6387946811924815</v>
+        <v>0.5525259015340134</v>
       </c>
       <c r="AL2">
-        <v>358.9</v>
+        <v>0.576</v>
       </c>
       <c r="AM2">
-        <v>325</v>
+        <v>-10.824</v>
       </c>
       <c r="AN2">
-        <v>19.08915806195393</v>
+        <v>33.34642857142858</v>
       </c>
       <c r="AO2">
-        <v>1.371412649763165</v>
+        <v>190.7986111111111</v>
       </c>
       <c r="AP2">
-        <v>14.62390786338363</v>
+        <v>24.56964285714286</v>
       </c>
       <c r="AQ2">
-        <v>1.514461538461539</v>
+        <v>-10.15336289726534</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0576</v>
+        <v>0.0518</v>
       </c>
       <c r="E3">
-        <v>0.124</v>
+        <v>0.101</v>
       </c>
       <c r="F3">
-        <v>0.08939999999999999</v>
+        <v>0.0935</v>
       </c>
       <c r="G3">
-        <v>0.6415730337078652</v>
+        <v>0.5711392405063291</v>
       </c>
       <c r="H3">
-        <v>0.5584269662921348</v>
+        <v>0.4977215189873417</v>
       </c>
       <c r="I3">
-        <v>0.499438202247191</v>
+        <v>0.5564556962025317</v>
       </c>
       <c r="J3">
-        <v>0.3604640937957988</v>
+        <v>0.4141848752369827</v>
       </c>
       <c r="K3">
-        <v>69.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L3">
-        <v>0.3904494382022472</v>
+        <v>0.4486075949367088</v>
       </c>
       <c r="M3">
-        <v>65.27</v>
+        <v>78.2</v>
       </c>
       <c r="N3">
-        <v>0.05844376790830946</v>
+        <v>0.07006540632559807</v>
       </c>
       <c r="O3">
-        <v>0.939136690647482</v>
+        <v>0.8826185101580136</v>
       </c>
       <c r="P3">
-        <v>58.3</v>
+        <v>63.2</v>
       </c>
       <c r="Q3">
-        <v>0.05220272206303725</v>
+        <v>0.05662575038079026</v>
       </c>
       <c r="R3">
-        <v>0.8388489208633093</v>
+        <v>0.7133182844243793</v>
       </c>
       <c r="S3">
-        <v>6.969999999999999</v>
+        <v>15</v>
       </c>
       <c r="T3">
-        <v>0.1067871916653899</v>
+        <v>0.1918158567774936</v>
       </c>
       <c r="U3">
-        <v>167.6</v>
+        <v>184.2</v>
       </c>
       <c r="V3">
-        <v>0.1500716332378224</v>
+        <v>0.1650389750022399</v>
       </c>
       <c r="W3">
-        <v>0.2207049857097491</v>
+        <v>0.2589885998246126</v>
       </c>
       <c r="X3">
-        <v>0.02611993572958583</v>
+        <v>0.05341384185885444</v>
       </c>
       <c r="Y3">
-        <v>0.1945850499801633</v>
+        <v>0.2055747579657582</v>
       </c>
       <c r="Z3">
-        <v>6.054421768707487</v>
+        <v>5.38147138964577</v>
       </c>
       <c r="AA3">
-        <v>2.182401656314702</v>
+        <v>2.228924056111825</v>
       </c>
       <c r="AB3">
-        <v>0.02611695782267276</v>
+        <v>0.05337800408171956</v>
       </c>
       <c r="AC3">
-        <v>2.156284698492029</v>
+        <v>2.175546052030105</v>
       </c>
       <c r="AD3">
-        <v>12.6</v>
+        <v>10.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>12.6</v>
+        <v>10.1</v>
       </c>
       <c r="AG3">
-        <v>-155</v>
+        <v>-174.1</v>
       </c>
       <c r="AH3">
-        <v>0.01115636621214804</v>
+        <v>0.008968211685313445</v>
       </c>
       <c r="AI3">
-        <v>0.03437926330150068</v>
+        <v>0.02620653866113129</v>
       </c>
       <c r="AJ3">
-        <v>-0.1611561655229778</v>
+        <v>-0.1848195329087049</v>
       </c>
       <c r="AK3">
-        <v>-0.7792860734037206</v>
+        <v>-0.8653081510934393</v>
       </c>
       <c r="AL3">
-        <v>16</v>
+        <v>0.576</v>
       </c>
       <c r="AM3">
-        <v>-7.600000000000001</v>
+        <v>-10.824</v>
       </c>
       <c r="AN3">
-        <v>0.1368078175895766</v>
+        <v>0.09017857142857143</v>
       </c>
       <c r="AO3">
-        <v>5.55625</v>
+        <v>190.7986111111111</v>
       </c>
       <c r="AP3">
-        <v>-1.682953311617807</v>
+        <v>-1.554464285714286</v>
       </c>
       <c r="AQ3">
-        <v>-11.69736842105263</v>
+        <v>-10.15336289726534</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unifin Financiera, S. A. B. de C. V. (BMV:UNIFIN A)</t>
+          <t>Gentera, S.A.B. de C.V. (BMV:GENTERA *)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -862,124 +862,112 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0582</v>
+        <v>0.051</v>
       </c>
       <c r="E4">
-        <v>0.0368</v>
+        <v>0.0819</v>
       </c>
       <c r="F4">
-        <v>0.212</v>
+        <v>0.321</v>
       </c>
       <c r="G4">
-        <v>0.7282938135139954</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.7282938135139954</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.7190229987520057</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0.553853144181545</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>67.40000000000001</v>
+        <v>227</v>
       </c>
       <c r="L4">
-        <v>0.1201640221073275</v>
+        <v>0.2140096162911285</v>
       </c>
       <c r="M4">
-        <v>45.5</v>
+        <v>27.07</v>
       </c>
       <c r="N4">
-        <v>0.05375073833431778</v>
+        <v>0.01520615661161667</v>
       </c>
       <c r="O4">
-        <v>0.6750741839762611</v>
+        <v>0.1192511013215859</v>
       </c>
       <c r="P4">
-        <v>12.1</v>
+        <v>23.4</v>
       </c>
       <c r="Q4">
-        <v>0.01429415239220319</v>
+        <v>0.01314459049544995</v>
       </c>
       <c r="R4">
-        <v>0.1795252225519288</v>
+        <v>0.1030837004405286</v>
       </c>
       <c r="S4">
-        <v>33.4</v>
+        <v>3.670000000000002</v>
       </c>
       <c r="T4">
-        <v>0.734065934065934</v>
+        <v>0.1355744366457333</v>
       </c>
       <c r="U4">
-        <v>191.8</v>
+        <v>509.2</v>
       </c>
       <c r="V4">
-        <v>0.2265800354400473</v>
+        <v>0.2860352769351758</v>
       </c>
       <c r="W4">
-        <v>0.1182248728293282</v>
+        <v>0.2291771832407875</v>
       </c>
       <c r="X4">
-        <v>0.05871991030451306</v>
+        <v>0.06094725237638184</v>
       </c>
       <c r="Y4">
-        <v>0.05950496252481514</v>
+        <v>0.1682299308644056</v>
       </c>
       <c r="Z4">
-        <v>0.1569258316313684</v>
+        <v>0.6885426809477444</v>
       </c>
       <c r="AA4">
-        <v>0.08691386525233713</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04329295735228349</v>
+        <v>0.05945587851241461</v>
       </c>
       <c r="AC4">
-        <v>0.04362090790005364</v>
+        <v>-0.05945587851241461</v>
       </c>
       <c r="AD4">
-        <v>3615.2</v>
+        <v>1335.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>3615.2</v>
+        <v>1335.4</v>
       </c>
       <c r="AG4">
-        <v>3423.4</v>
+        <v>826.2</v>
       </c>
       <c r="AH4">
-        <v>0.810274110764955</v>
+        <v>0.428617280780588</v>
       </c>
       <c r="AI4">
-        <v>0.851456699404131</v>
+        <v>0.5163161150634086</v>
       </c>
       <c r="AJ4">
-        <v>0.8017517974659828</v>
+        <v>0.3169889502762431</v>
       </c>
       <c r="AK4">
-        <v>0.84442909647024</v>
+        <v>0.3977469670710572</v>
       </c>
       <c r="AL4">
-        <v>342.9</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>332.6</v>
-      </c>
-      <c r="AN4">
-        <v>8.785419198055893</v>
-      </c>
-      <c r="AO4">
-        <v>1.176144648585594</v>
-      </c>
-      <c r="AP4">
-        <v>8.319319562575942</v>
-      </c>
-      <c r="AQ4">
-        <v>1.21256764882742</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -990,7 +978,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Monex, S.A.B. de C.V. (BMV:MONEX B)</t>
+          <t>INVEX Controladora, S.A.B. de C.V. (BMV:INVEX A)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -999,10 +987,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.08470000000000001</v>
+        <v>0.0761</v>
       </c>
       <c r="E5">
-        <v>-0.0171</v>
+        <v>0.116</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1017,456 +1005,90 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>37.3</v>
+        <v>64.5</v>
       </c>
       <c r="L5">
-        <v>0.08923444976076554</v>
+        <v>0.2765866209262436</v>
       </c>
       <c r="M5">
-        <v>8.800000000000001</v>
+        <v>3.59</v>
       </c>
       <c r="N5">
-        <v>0.02871125611745514</v>
+        <v>0.00574583866837388</v>
       </c>
       <c r="O5">
-        <v>0.2359249329758714</v>
+        <v>0.05565891472868217</v>
       </c>
       <c r="P5">
-        <v>3.42</v>
+        <v>3.59</v>
       </c>
       <c r="Q5">
-        <v>0.01115823817292006</v>
+        <v>0.00574583866837388</v>
       </c>
       <c r="R5">
-        <v>0.09168900804289545</v>
+        <v>0.05565891472868217</v>
       </c>
       <c r="S5">
-        <v>5.380000000000001</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.6113636363636364</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1205.9</v>
+        <v>289.6</v>
       </c>
       <c r="V5">
-        <v>3.93442088091354</v>
+        <v>0.4635083226632523</v>
       </c>
       <c r="W5">
-        <v>0.07244125072829675</v>
+        <v>0.1199107640825432</v>
       </c>
       <c r="X5">
-        <v>0.03041843699394147</v>
+        <v>0.09219500097851259</v>
       </c>
       <c r="Y5">
-        <v>0.04202281373435528</v>
+        <v>0.02771576310403064</v>
       </c>
       <c r="Z5">
-        <v>3.650655021834061</v>
+        <v>0.1032818105319102</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.03070973995733649</v>
+        <v>0.06466644675572161</v>
       </c>
       <c r="AC5">
-        <v>-0.03070973995733649</v>
+        <v>-0.06466644675572161</v>
       </c>
       <c r="AD5">
-        <v>175.6</v>
+        <v>2389.3</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>175.6</v>
+        <v>2389.3</v>
       </c>
       <c r="AG5">
-        <v>-1030.3</v>
+        <v>2099.7</v>
       </c>
       <c r="AH5">
-        <v>0.3642397842771209</v>
+        <v>0.7927076075777181</v>
       </c>
       <c r="AI5">
-        <v>0.2334175196065399</v>
+        <v>0.7986696082363952</v>
       </c>
       <c r="AJ5">
-        <v>1.4234595192042</v>
+        <v>0.7706735180767115</v>
       </c>
       <c r="AK5">
-        <v>2.271384479717813</v>
+        <v>0.7770910436713546</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Gentera, S.A.B. de C.V. (BMV:GENTERA *)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.00949</v>
-      </c>
-      <c r="E6">
-        <v>-0.136</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="L6">
-        <v>0.1033585619678335</v>
-      </c>
-      <c r="M6">
-        <v>-0</v>
-      </c>
-      <c r="N6">
-        <v>-0</v>
-      </c>
-      <c r="O6">
-        <v>-0</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>-0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>431.2</v>
-      </c>
-      <c r="V6">
-        <v>0.4224551778191437</v>
-      </c>
-      <c r="W6">
-        <v>0.101888552110049</v>
-      </c>
-      <c r="X6">
-        <v>0.03508328068546727</v>
-      </c>
-      <c r="Y6">
-        <v>0.0668052714245817</v>
-      </c>
-      <c r="Z6">
-        <v>0.5812882381246993</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.03183371314732601</v>
-      </c>
-      <c r="AC6">
-        <v>-0.03183371314732601</v>
-      </c>
-      <c r="AD6">
-        <v>1206.9</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>1206.9</v>
-      </c>
-      <c r="AG6">
-        <v>775.7</v>
-      </c>
-      <c r="AH6">
-        <v>0.541793858861555</v>
-      </c>
-      <c r="AI6">
-        <v>0.509240506329114</v>
-      </c>
-      <c r="AJ6">
-        <v>0.4318080605655756</v>
-      </c>
-      <c r="AK6">
-        <v>0.4000928409325356</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>INVEX Controladora, S.A.B. de C.V. (BMV:INVEX A)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.118</v>
-      </c>
-      <c r="E7">
-        <v>0.135</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>51.6</v>
-      </c>
-      <c r="L7">
-        <v>0.2483156881616939</v>
-      </c>
-      <c r="M7">
-        <v>6.13</v>
-      </c>
-      <c r="N7">
-        <v>0.0106553102729011</v>
-      </c>
-      <c r="O7">
-        <v>0.1187984496124031</v>
-      </c>
-      <c r="P7">
-        <v>6.13</v>
-      </c>
-      <c r="Q7">
-        <v>0.0106553102729011</v>
-      </c>
-      <c r="R7">
-        <v>0.1187984496124031</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>207.8</v>
-      </c>
-      <c r="V7">
-        <v>0.3612028506865984</v>
-      </c>
-      <c r="W7">
-        <v>0.1117608836907083</v>
-      </c>
-      <c r="X7">
-        <v>0.05168009900038593</v>
-      </c>
-      <c r="Y7">
-        <v>0.06008078469032233</v>
-      </c>
-      <c r="Z7">
-        <v>0.2307606885063853</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.03592105527710165</v>
-      </c>
-      <c r="AC7">
-        <v>-0.03592105527710165</v>
-      </c>
-      <c r="AD7">
-        <v>1927.8</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>1927.8</v>
-      </c>
-      <c r="AG7">
-        <v>1720</v>
-      </c>
-      <c r="AH7">
-        <v>0.7701649954056969</v>
-      </c>
-      <c r="AI7">
-        <v>0.7818469400170337</v>
-      </c>
-      <c r="AJ7">
-        <v>0.749357382477236</v>
-      </c>
-      <c r="AK7">
-        <v>0.7617697860844147</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Crédito Real, S.A.B. de C.V., Sociedad Financiera de Objeto Múltiple, Entidad No Regulada (BMV:CREAL *)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>-0.0136</v>
-      </c>
-      <c r="E8">
-        <v>-0.19</v>
-      </c>
-      <c r="F8">
-        <v>0.157</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>29.6</v>
-      </c>
-      <c r="L8">
-        <v>0.1256366723259763</v>
-      </c>
-      <c r="M8">
-        <v>34.3</v>
-      </c>
-      <c r="N8">
-        <v>0.2390243902439024</v>
-      </c>
-      <c r="O8">
-        <v>1.158783783783784</v>
-      </c>
-      <c r="P8">
-        <v>18.3</v>
-      </c>
-      <c r="Q8">
-        <v>0.1275261324041812</v>
-      </c>
-      <c r="R8">
-        <v>0.6182432432432432</v>
-      </c>
-      <c r="S8">
-        <v>16</v>
-      </c>
-      <c r="T8">
-        <v>0.466472303206997</v>
-      </c>
-      <c r="U8">
-        <v>44.4</v>
-      </c>
-      <c r="V8">
-        <v>0.3094076655052265</v>
-      </c>
-      <c r="W8">
-        <v>0.03932509631991497</v>
-      </c>
-      <c r="X8">
-        <v>0.1687142309192972</v>
-      </c>
-      <c r="Y8">
-        <v>-0.1293891345993822</v>
-      </c>
-      <c r="Z8">
-        <v>0.07565831727681438</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.04855693742866288</v>
-      </c>
-      <c r="AC8">
-        <v>-0.04855693742866288</v>
-      </c>
-      <c r="AD8">
-        <v>2675.2</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>2675.2</v>
-      </c>
-      <c r="AG8">
-        <v>2630.8</v>
-      </c>
-      <c r="AH8">
-        <v>0.9490900060311491</v>
-      </c>
-      <c r="AI8">
-        <v>0.7478474784747847</v>
-      </c>
-      <c r="AJ8">
-        <v>0.9482752406012327</v>
-      </c>
-      <c r="AK8">
-        <v>0.7446784420289855</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/mexico/mexico_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_financial_svcs_non_bank_insurance.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0518</v>
+        <v>0.0616</v>
       </c>
       <c r="E2">
-        <v>0.101</v>
+        <v>0.111</v>
       </c>
       <c r="F2">
-        <v>0.20725</v>
+        <v>0.08905</v>
       </c>
       <c r="G2">
-        <v>0.0756336328282151</v>
+        <v>0.06617609221427469</v>
       </c>
       <c r="H2">
-        <v>0.06591122435295695</v>
+        <v>0.05665620336540935</v>
       </c>
       <c r="I2">
-        <v>0.07368915113316347</v>
+        <v>0.05367158956414347</v>
       </c>
       <c r="J2">
-        <v>0.05469819686103484</v>
+        <v>0.03686723123945509</v>
       </c>
       <c r="K2">
-        <v>380.1</v>
+        <v>405.2</v>
       </c>
       <c r="L2">
-        <v>0.2548612042376291</v>
+        <v>0.2085112952194721</v>
       </c>
       <c r="M2">
-        <v>108.86</v>
+        <v>145.3266</v>
       </c>
       <c r="N2">
-        <v>0.03091647496520974</v>
+        <v>0.03483129209309014</v>
       </c>
       <c r="O2">
-        <v>0.2863983162325703</v>
+        <v>0.3586539980256663</v>
       </c>
       <c r="P2">
-        <v>90.19</v>
+        <v>128.4266</v>
       </c>
       <c r="Q2">
-        <v>0.02561415466757547</v>
+        <v>0.03078076840112168</v>
       </c>
       <c r="R2">
-        <v>0.2372796632465141</v>
+        <v>0.3169461994076999</v>
       </c>
       <c r="S2">
-        <v>18.67</v>
+        <v>16.89999999999999</v>
       </c>
       <c r="T2">
-        <v>0.1715046849164064</v>
+        <v>0.116289791407767</v>
       </c>
       <c r="U2">
-        <v>983</v>
+        <v>1163.9</v>
       </c>
       <c r="V2">
-        <v>0.2791741217233251</v>
+        <v>0.2789588476379934</v>
       </c>
       <c r="W2">
-        <v>0.2291771832407875</v>
+        <v>0.2204021494193101</v>
       </c>
       <c r="X2">
-        <v>0.06094725237638184</v>
+        <v>0.06733091256644945</v>
       </c>
       <c r="Y2">
-        <v>0.1682299308644056</v>
+        <v>0.1530712368528607</v>
       </c>
       <c r="Z2">
-        <v>0.3888816458501735</v>
+        <v>0.4358230244094983</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05945587851241461</v>
+        <v>0.05739439440902255</v>
       </c>
       <c r="AC2">
-        <v>-0.05945587851241461</v>
+        <v>-0.05739439440902255</v>
       </c>
       <c r="AD2">
-        <v>3734.8</v>
+        <v>5357</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3734.8</v>
+        <v>5357</v>
       </c>
       <c r="AG2">
-        <v>2751.8</v>
+        <v>4193.1</v>
       </c>
       <c r="AH2">
-        <v>0.5147259471602421</v>
+        <v>0.5621609142329448</v>
       </c>
       <c r="AI2">
-        <v>0.6262870174732535</v>
+        <v>0.6639893900519342</v>
       </c>
       <c r="AJ2">
-        <v>0.4386806740104259</v>
+        <v>0.5012432161044301</v>
       </c>
       <c r="AK2">
-        <v>0.5525259015340134</v>
+        <v>0.6073435689455389</v>
       </c>
       <c r="AL2">
-        <v>0.576</v>
+        <v>0.729</v>
       </c>
       <c r="AM2">
-        <v>-10.824</v>
+        <v>-22.371</v>
       </c>
       <c r="AN2">
-        <v>33.34642857142858</v>
+        <v>53.03960396039604</v>
       </c>
       <c r="AO2">
-        <v>190.7986111111111</v>
+        <v>143.0727023319616</v>
       </c>
       <c r="AP2">
-        <v>24.56964285714286</v>
+        <v>41.51584158415842</v>
       </c>
       <c r="AQ2">
-        <v>-10.15336289726534</v>
+        <v>-4.662285995261723</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0518</v>
+        <v>0.0214</v>
       </c>
       <c r="E3">
-        <v>0.101</v>
+        <v>0.0199</v>
       </c>
       <c r="F3">
-        <v>0.0935</v>
+        <v>0.0381</v>
       </c>
       <c r="G3">
-        <v>0.5711392405063291</v>
+        <v>0.6051764705882353</v>
       </c>
       <c r="H3">
-        <v>0.4977215189873417</v>
+        <v>0.5181176470588235</v>
       </c>
       <c r="I3">
-        <v>0.5564556962025317</v>
+        <v>0.4908235294117647</v>
       </c>
       <c r="J3">
-        <v>0.4141848752369827</v>
+        <v>0.3398564688568584</v>
       </c>
       <c r="K3">
-        <v>88.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="L3">
-        <v>0.4486075949367088</v>
+        <v>0.4</v>
       </c>
       <c r="M3">
-        <v>78.2</v>
+        <v>93.19999999999999</v>
       </c>
       <c r="N3">
-        <v>0.07006540632559807</v>
+        <v>0.07864978902953586</v>
       </c>
       <c r="O3">
-        <v>0.8826185101580136</v>
+        <v>1.096470588235294</v>
       </c>
       <c r="P3">
-        <v>63.2</v>
+        <v>76.3</v>
       </c>
       <c r="Q3">
-        <v>0.05662575038079026</v>
+        <v>0.06438818565400843</v>
       </c>
       <c r="R3">
-        <v>0.7133182844243793</v>
+        <v>0.8976470588235294</v>
       </c>
       <c r="S3">
-        <v>15</v>
+        <v>16.89999999999999</v>
       </c>
       <c r="T3">
-        <v>0.1918158567774936</v>
+        <v>0.1813304721030042</v>
       </c>
       <c r="U3">
-        <v>184.2</v>
+        <v>202.3</v>
       </c>
       <c r="V3">
-        <v>0.1650389750022399</v>
+        <v>0.1707172995780591</v>
       </c>
       <c r="W3">
-        <v>0.2589885998246126</v>
+        <v>0.2378953260565351</v>
       </c>
       <c r="X3">
-        <v>0.05341384185885444</v>
+        <v>0.0566651430723206</v>
       </c>
       <c r="Y3">
-        <v>0.2055747579657582</v>
+        <v>0.1812301829842145</v>
       </c>
       <c r="Z3">
-        <v>5.38147138964577</v>
+        <v>7.154882154882144</v>
       </c>
       <c r="AA3">
-        <v>2.228924056111825</v>
+        <v>2.431632984245196</v>
       </c>
       <c r="AB3">
-        <v>0.05337800408171956</v>
+        <v>0.05651414674163646</v>
       </c>
       <c r="AC3">
-        <v>2.175546052030105</v>
+        <v>2.375118837503559</v>
       </c>
       <c r="AD3">
-        <v>10.1</v>
+        <v>17.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>10.1</v>
+        <v>17.1</v>
       </c>
       <c r="AG3">
-        <v>-174.1</v>
+        <v>-185.2</v>
       </c>
       <c r="AH3">
-        <v>0.008968211685313445</v>
+        <v>0.01422510606438732</v>
       </c>
       <c r="AI3">
-        <v>0.02620653866113129</v>
+        <v>0.0389344262295082</v>
       </c>
       <c r="AJ3">
-        <v>-0.1848195329087049</v>
+        <v>-0.1852370474094819</v>
       </c>
       <c r="AK3">
-        <v>-0.8653081510934393</v>
+        <v>-0.7817644575770368</v>
       </c>
       <c r="AL3">
-        <v>0.576</v>
+        <v>0.729</v>
       </c>
       <c r="AM3">
-        <v>-10.824</v>
+        <v>-22.371</v>
       </c>
       <c r="AN3">
-        <v>0.09017857142857143</v>
+        <v>0.1693069306930693</v>
       </c>
       <c r="AO3">
-        <v>190.7986111111111</v>
+        <v>143.0727023319616</v>
       </c>
       <c r="AP3">
-        <v>-1.554464285714286</v>
+        <v>-1.833663366336634</v>
       </c>
       <c r="AQ3">
-        <v>-10.15336289726534</v>
+        <v>-4.662285995261723</v>
       </c>
     </row>
     <row r="4">
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.051</v>
+        <v>0.0616</v>
       </c>
       <c r="E4">
-        <v>0.0819</v>
+        <v>0.111</v>
       </c>
       <c r="F4">
-        <v>0.321</v>
+        <v>0.14</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -883,85 +883,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>227</v>
+        <v>254.3</v>
       </c>
       <c r="L4">
-        <v>0.2140096162911285</v>
+        <v>0.1899036666417744</v>
       </c>
       <c r="M4">
-        <v>27.07</v>
+        <v>52.11360000000001</v>
       </c>
       <c r="N4">
-        <v>0.01520615661161667</v>
+        <v>0.02365896399872884</v>
       </c>
       <c r="O4">
-        <v>0.1192511013215859</v>
+        <v>0.2049296106960283</v>
       </c>
       <c r="P4">
-        <v>23.4</v>
+        <v>52.11360000000001</v>
       </c>
       <c r="Q4">
-        <v>0.01314459049544995</v>
+        <v>0.02365896399872884</v>
       </c>
       <c r="R4">
-        <v>0.1030837004405286</v>
+        <v>0.2049296106960283</v>
       </c>
       <c r="S4">
-        <v>3.670000000000002</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.1355744366457333</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>509.2</v>
+        <v>754</v>
       </c>
       <c r="V4">
-        <v>0.2860352769351758</v>
+        <v>0.3423071684750534</v>
       </c>
       <c r="W4">
-        <v>0.2291771832407875</v>
+        <v>0.2204021494193101</v>
       </c>
       <c r="X4">
-        <v>0.06094725237638184</v>
+        <v>0.06733091256644945</v>
       </c>
       <c r="Y4">
-        <v>0.1682299308644056</v>
+        <v>0.1530712368528607</v>
       </c>
       <c r="Z4">
-        <v>0.6885426809477444</v>
+        <v>0.7731970668052428</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05945587851241461</v>
+        <v>0.05739439440902255</v>
       </c>
       <c r="AC4">
-        <v>-0.05945587851241461</v>
+        <v>-0.05739439440902255</v>
       </c>
       <c r="AD4">
-        <v>1335.4</v>
+        <v>1929.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1335.4</v>
+        <v>1929.4</v>
       </c>
       <c r="AG4">
-        <v>826.2</v>
+        <v>1175.4</v>
       </c>
       <c r="AH4">
-        <v>0.428617280780588</v>
+        <v>0.4669296483628179</v>
       </c>
       <c r="AI4">
-        <v>0.5163161150634086</v>
+        <v>0.5556067499856016</v>
       </c>
       <c r="AJ4">
-        <v>0.3169889502762431</v>
+        <v>0.3479470708386371</v>
       </c>
       <c r="AK4">
-        <v>0.3977469670710572</v>
+        <v>0.4323548885455749</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0761</v>
+        <v>0.197</v>
       </c>
       <c r="E5">
-        <v>0.116</v>
+        <v>0.148</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1005,28 +1005,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>64.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="L5">
-        <v>0.2765866209262436</v>
+        <v>0.1682410007658923</v>
       </c>
       <c r="M5">
-        <v>3.59</v>
+        <v>0.013</v>
       </c>
       <c r="N5">
-        <v>0.00574583866837388</v>
+        <v>1.656895233239867e-05</v>
       </c>
       <c r="O5">
-        <v>0.05565891472868217</v>
+        <v>0.0001972685887708649</v>
       </c>
       <c r="P5">
-        <v>3.59</v>
+        <v>0.013</v>
       </c>
       <c r="Q5">
-        <v>0.00574583866837388</v>
+        <v>1.656895233239867e-05</v>
       </c>
       <c r="R5">
-        <v>0.05565891472868217</v>
+        <v>0.0001972685887708649</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1035,55 +1035,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>289.6</v>
+        <v>207.6</v>
       </c>
       <c r="V5">
-        <v>0.4635083226632523</v>
+        <v>0.2645934234004588</v>
       </c>
       <c r="W5">
-        <v>0.1199107640825432</v>
+        <v>0.1094139133322265</v>
       </c>
       <c r="X5">
-        <v>0.09219500097851259</v>
+        <v>0.1103022342083455</v>
       </c>
       <c r="Y5">
-        <v>0.02771576310403064</v>
+        <v>-0.0008883208761190503</v>
       </c>
       <c r="Z5">
-        <v>0.1032818105319102</v>
+        <v>0.1452182166001809</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06466644675572161</v>
+        <v>0.06289361905980255</v>
       </c>
       <c r="AC5">
-        <v>-0.06466644675572161</v>
+        <v>-0.06289361905980255</v>
       </c>
       <c r="AD5">
-        <v>2389.3</v>
+        <v>3410.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>2389.3</v>
+        <v>3410.5</v>
       </c>
       <c r="AG5">
-        <v>2099.7</v>
+        <v>3202.9</v>
       </c>
       <c r="AH5">
-        <v>0.7927076075777181</v>
+        <v>0.81297227718052</v>
       </c>
       <c r="AI5">
-        <v>0.7986696082363952</v>
+        <v>0.8206010442482135</v>
       </c>
       <c r="AJ5">
-        <v>0.7706735180767115</v>
+        <v>0.8032351097178684</v>
       </c>
       <c r="AK5">
-        <v>0.7770910436713546</v>
+        <v>0.8111687982778271</v>
       </c>
       <c r="AL5">
         <v>0</v>
